--- a/data/org-chart.xlsx
+++ b/data/org-chart.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
           <t>team</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,7 @@
           <t>ESS Claims</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -527,6 +534,7 @@
           <t>Continuous Improvement</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -554,6 +562,7 @@
           <t>Operations</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -581,6 +590,7 @@
           <t>Continuous Improvement</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,6 +618,7 @@
           <t>Continuous Improvement</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -635,6 +646,7 @@
           <t>Continuous Improvement</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -662,6 +674,7 @@
           <t>Operations</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -689,6 +702,7 @@
           <t>Operations</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -701,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -797,6 +811,13 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>photo       Optional profile image URL (leave blank for placeholder).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/org-chart.xlsx
+++ b/data/org-chart.xlsx
@@ -27,18 +27,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="0000008F"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="10"/>
@@ -441,15 +442,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +482,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>pillar</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>photo</t>
         </is>
       </c>
@@ -492,7 +499,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alex Morgan</t>
+          <t>Paulina Strozyk-Kozlowska</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,10 +510,15 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ESS Claims</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>leadership</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,12 +528,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jordan Lee</t>
+          <t>Rebecca Newcastle</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Continuous Improvement Lead</t>
+          <t>ESS Claims CI Lead</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -531,10 +543,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>leadership</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,25 +561,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Deekshith Kiran</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Operations Excellence Manager</t>
+          <t>Pillar Co-Lead</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -572,12 +594,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Casey Nguyen</t>
+          <t>Michele Panek</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Process Analyst</t>
+          <t>Pillar Lead</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,10 +609,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -600,12 +627,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Riley Patel</t>
+          <t>Vandana Taneja</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Process Analyst</t>
+          <t>Pillar Lead</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -615,10 +642,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>Process Improvement</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -628,12 +660,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Taylor Brooks</t>
+          <t>Smriti Kandari</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Change Manager</t>
+          <t>Pillar Lead</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -643,10 +675,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,25 +693,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Morgan Ellis</t>
+          <t>Anna Rzepka</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quality Lead</t>
+          <t>System Enhancement</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -684,25 +726,492 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jamie Chen</t>
+          <t>Sudha S.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>System Enhancement</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pracilla Ullas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ayushi Choudhary</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Oktawia Marynowska</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>System Enhancement</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Priyanka Kapoor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Process Improvement</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Process Improvement</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nehal Sharma</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Process Improvement</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Process Improvement</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dinesh Sanmugam</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Process Improvement</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Process Improvement</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jasno John</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Meghana Gowda</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Automation, BI &amp; Reporting Jr.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deepak M.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Shivashankar V.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Anshul Chhabra</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mehak Verma</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ashutosh Uniyal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -715,10 +1224,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,7 +1243,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>1. Edit names, roles, or teams on the 'Org Chart' sheet.</t>
+          <t>1. Edit names, roles, teams, or pillars on the 'Org Chart' sheet.</t>
         </is>
       </c>
     </row>
@@ -762,59 +1271,108 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>5. Commit and push this file to GitHub. Pages rebuilds the chart.</t>
+          <t>5. pillar must be one of: leadership | system | process | automation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>6. Photos:</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Columns:</t>
+          <t xml:space="preserve">   a) Put image files in assets/photos/ (jpg/png/webp).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>id          Unique identifier (text or number).</t>
+          <t xml:space="preserve">   b) In the photo column, enter the filename only, e.g. rebecca.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>name        Display name on the chart card.</t>
+          <t xml:space="preserve">      OR a full https:// image URL.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>role        Job title / role line under the name.</t>
+          <t xml:space="preserve">   c) Leave photo blank to keep the square placeholder.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>manager_id  id of the manager; blank for the root.</t>
+          <t>7. Commit and push. GitHub Pages rebuilds the chart.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>team        Optional team / department label.</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>photo       Optional profile image URL (leave blank for placeholder).</t>
+          <t>Columns:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>id          Unique identifier (text or number).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>name        Display name on the chart card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>role        Job title / role line under the name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>manager_id  id of the manager; blank for the root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>team        Team / department label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>pillar      leadership | system | process | automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>photo       Filename in assets/photos/ OR image URL.</t>
         </is>
       </c>
     </row>
